--- a/data/trans_orig/IP07A19-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07A19-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que le haya gustado ir al colegio en 2007 (tasa de respuesta: 99,2%)</t>
+          <t>Menores según la frecuencia de que le haya gustado ir al colegio, percibida por el adulto en 2007 (tasa de respuesta: 99,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42590</t>
+          <t>42275</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60101</t>
+          <t>60111</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27674</t>
+          <t>29293</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45089</t>
+          <t>46527</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>76356</t>
+          <t>74925</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>100892</t>
+          <t>100281</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,44%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45911</t>
+          <t>45962</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64361</t>
+          <t>64719</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50588</t>
+          <t>50583</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69359</t>
+          <t>69554</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>101790</t>
+          <t>101386</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>128992</t>
+          <t>128471</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>47,96%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11394</t>
+          <t>11068</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23361</t>
+          <t>23987</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24250</t>
+          <t>24478</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39795</t>
+          <t>39894</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>39539</t>
+          <t>38767</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>58961</t>
+          <t>59801</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,32%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7191</t>
+          <t>6907</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2924</t>
+          <t>2950</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11112</t>
+          <t>11624</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>5281</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15253</t>
+          <t>14875</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>4847</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2598</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10300</t>
+          <t>10617</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>3288</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12171</t>
+          <t>12266</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37203</t>
+          <t>37252</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57752</t>
+          <t>56883</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29610</t>
+          <t>30068</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47738</t>
+          <t>48587</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>70259</t>
+          <t>71548</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>97499</t>
+          <t>98551</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,89%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84435</t>
+          <t>85803</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>108480</t>
+          <t>108534</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>81298</t>
+          <t>80252</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>104197</t>
+          <t>104092</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>173569</t>
+          <t>174523</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>206320</t>
+          <t>205388</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>51,88%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24526</t>
+          <t>24375</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41578</t>
+          <t>41060</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>42113</t>
+          <t>41365</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>60984</t>
+          <t>61563</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>72473</t>
+          <t>72427</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>97968</t>
+          <t>98450</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,87%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2827</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11822</t>
+          <t>11416</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9593</t>
+          <t>9932</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21898</t>
+          <t>21858</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15465</t>
+          <t>14780</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30118</t>
+          <t>29492</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6725</t>
+          <t>5837</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17060</t>
+          <t>16121</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>2612</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10933</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10792</t>
+          <t>11191</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23152</t>
+          <t>24343</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>85173</t>
+          <t>83809</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>110797</t>
+          <t>110781</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>63538</t>
+          <t>63770</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>89369</t>
+          <t>87201</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>154169</t>
+          <t>155151</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>191702</t>
+          <t>190342</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,68%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>136482</t>
+          <t>137355</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>164732</t>
+          <t>166385</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,82 +2224,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>42,9%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>51,97%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>152606</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>137586</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>167172</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>44,41%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>40,04%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>48,65%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>304175</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>282951</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>326760</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>45,83%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>42,63%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>51,45%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>152606</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>138574</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>167432</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>40,33%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>48,73%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>453</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>304175</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>282896</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>325099</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>45,83%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>42,62%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>49,23%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>40472</t>
+          <t>39814</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>61473</t>
+          <t>60500</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>69270</t>
+          <t>71119</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>94924</t>
+          <t>97400</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>116438</t>
+          <t>117505</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>148641</t>
+          <t>150349</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5399</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15483</t>
+          <t>15516</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14871</t>
+          <t>15054</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30350</t>
+          <t>29753</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22742</t>
+          <t>23044</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>40791</t>
+          <t>40010</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7176</t>
+          <t>7235</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18449</t>
+          <t>18948</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6467</t>
+          <t>6760</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17777</t>
+          <t>17359</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17114</t>
+          <t>17375</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>32088</t>
+          <t>32517</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que le haya gustado ir al colegio en 2012 (tasa de respuesta: 98,02%)</t>
+          <t>Menores según la frecuencia de que le haya gustado ir al colegio, percibida por el adulto en 2012 (tasa de respuesta: 98,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>68223</t>
+          <t>67154</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>88981</t>
+          <t>88281</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56891</t>
+          <t>57183</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>75699</t>
+          <t>77968</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>129726</t>
+          <t>129806</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>159174</t>
+          <t>158882</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>50,89%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48885</t>
+          <t>47868</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69319</t>
+          <t>68071</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49202</t>
+          <t>49652</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69237</t>
+          <t>69157</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>103276</t>
+          <t>104124</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>131840</t>
+          <t>132249</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,36%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8438</t>
+          <t>8113</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20450</t>
+          <t>20594</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12156</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25784</t>
+          <t>25195</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23192</t>
+          <t>22401</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>39985</t>
+          <t>40250</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8722</t>
+          <t>8749</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5177</t>
+          <t>5303</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14603</t>
+          <t>15535</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8521</t>
+          <t>8565</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19679</t>
+          <t>19477</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>651</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>6297</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7893</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>2643</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11301</t>
+          <t>11050</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47676</t>
+          <t>48014</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67395</t>
+          <t>67072</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43050</t>
+          <t>43336</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63211</t>
+          <t>62968</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>96378</t>
+          <t>97304</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>125175</t>
+          <t>124927</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,57%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58631</t>
+          <t>57268</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>79087</t>
+          <t>78550</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59997</t>
+          <t>61714</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>80848</t>
+          <t>83046</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>125633</t>
+          <t>124548</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>154871</t>
+          <t>154294</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,16%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21468</t>
+          <t>21522</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37952</t>
+          <t>37808</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23599</t>
+          <t>24439</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>40874</t>
+          <t>40469</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>49774</t>
+          <t>50640</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>74402</t>
+          <t>73961</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,65%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>3469</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11687</t>
+          <t>12528</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7902</t>
+          <t>7350</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19159</t>
+          <t>19112</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13314</t>
+          <t>13672</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28072</t>
+          <t>27000</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1871</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8269</t>
+          <t>8891</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3628</t>
+          <t>3551</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12178</t>
+          <t>12266</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6798</t>
+          <t>7175</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17445</t>
+          <t>18048</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>120095</t>
+          <t>120696</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>149921</t>
+          <t>149292</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>105042</t>
+          <t>104501</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>134157</t>
+          <t>132896</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>231952</t>
+          <t>233502</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>272900</t>
+          <t>273217</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,79%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>111005</t>
+          <t>111892</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>140054</t>
+          <t>141332</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>116244</t>
+          <t>117260</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>146264</t>
+          <t>147285</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>237775</t>
+          <t>238457</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>278430</t>
+          <t>279346</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,73%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32706</t>
+          <t>32896</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>53603</t>
+          <t>54118</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40840</t>
+          <t>40144</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>61381</t>
+          <t>61728</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>77091</t>
+          <t>78422</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>106996</t>
+          <t>106689</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,32%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17448</t>
+          <t>17961</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16071</t>
+          <t>15284</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30684</t>
+          <t>30280</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24663</t>
+          <t>24675</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>42614</t>
+          <t>43643</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3237</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11752</t>
+          <t>11985</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6795</t>
+          <t>6221</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16772</t>
+          <t>16929</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>11989</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>25407</t>
+          <t>24955</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que le haya gustado ir al colegio en 2016 (tasa de respuesta: 98,62%)</t>
+          <t>Menores según la frecuencia de que le haya gustado ir al colegio, percibida por el adulto en 2016 (tasa de respuesta: 98,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74829</t>
+          <t>74362</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>97126</t>
+          <t>96653</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>70459</t>
+          <t>71847</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>92359</t>
+          <t>93602</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>151475</t>
+          <t>151608</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>184847</t>
+          <t>182652</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,3%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56120</t>
+          <t>56776</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77972</t>
+          <t>77927</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52502</t>
+          <t>52364</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73376</t>
+          <t>73808</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>114048</t>
+          <t>113876</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>145983</t>
+          <t>145496</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,27%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17608</t>
+          <t>17087</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32256</t>
+          <t>32060</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20490</t>
+          <t>20533</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37345</t>
+          <t>36446</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>42265</t>
+          <t>41490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>64631</t>
+          <t>63707</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,19%</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>2879</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12329</t>
+          <t>11962</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3868</t>
+          <t>3985</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13426</t>
+          <t>13220</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8887</t>
+          <t>9157</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21985</t>
+          <t>22030</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>659</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6650</t>
+          <t>6513</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10488</t>
+          <t>9820</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>4164</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13297</t>
+          <t>13891</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52669</t>
+          <t>53039</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74383</t>
+          <t>73618</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38144</t>
+          <t>37542</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58355</t>
+          <t>58684</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>95297</t>
+          <t>97377</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>125277</t>
+          <t>126498</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,68%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55691</t>
+          <t>54882</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>77288</t>
+          <t>75848</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65044</t>
+          <t>65503</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>87502</t>
+          <t>86078</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>125976</t>
+          <t>127015</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>157841</t>
+          <t>157217</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>45,59%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22877</t>
+          <t>23791</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>40648</t>
+          <t>40288</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30769</t>
+          <t>30077</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>48905</t>
+          <t>48710</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>57615</t>
+          <t>59113</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>83414</t>
+          <t>83674</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,26%</t>
         </is>
       </c>
     </row>
@@ -6305,12 +6305,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3333</t>
+          <t>3370</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12274</t>
+          <t>11887</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6320,12 +6320,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5065</t>
+          <t>5224</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15766</t>
+          <t>15489</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6355,12 +6355,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11023</t>
+          <t>10826</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24389</t>
+          <t>24100</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -6418,12 +6418,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9261</t>
+          <t>8468</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>629</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5450</t>
+          <t>5395</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>2776</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11018</t>
+          <t>11260</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6503,12 +6503,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>134608</t>
+          <t>135310</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>164484</t>
+          <t>165324</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>114494</t>
+          <t>114693</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>144312</t>
+          <t>144308</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>255471</t>
+          <t>256098</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>300320</t>
+          <t>299026</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>41,8%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>117130</t>
+          <t>118538</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>146496</t>
+          <t>147470</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>125131</t>
+          <t>124475</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>156677</t>
+          <t>154859</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>248439</t>
+          <t>251404</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>294022</t>
+          <t>292480</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>40,89%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>44977</t>
+          <t>44990</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>67588</t>
+          <t>67441</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>54409</t>
+          <t>55405</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>81001</t>
+          <t>79626</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>106757</t>
+          <t>106447</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>141851</t>
+          <t>141391</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,76%</t>
         </is>
       </c>
     </row>
@@ -6987,12 +6987,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8040</t>
+          <t>8088</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19618</t>
+          <t>20035</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11096</t>
+          <t>11246</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25269</t>
+          <t>24424</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7037,12 +7037,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22490</t>
+          <t>22158</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>40722</t>
+          <t>40372</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -7100,12 +7100,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3237</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12550</t>
+          <t>11096</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3832</t>
+          <t>3472</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13208</t>
+          <t>12709</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7150,12 +7150,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8269</t>
+          <t>8187</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20571</t>
+          <t>20822</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07A19-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07A19-Edad-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de que le haya gustado ir al colegio, percibida por el adulto en 2007 (tasa de respuesta: 99,2%)</t>
+          <t>Menores según la frecuencia de que le haya gustado ir al colegio, percibida por el/la adulto/a [KIDSCREEN 20] en 2007 (tasa de respuesta: 99,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>36999</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>29499</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>46250</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>26,37%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>21,02%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>32,96%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>50990</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>42275</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>60111</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>41789</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>59800</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>39,98%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>33,14%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>47,13%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>36999</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>29293</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>46527</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>26,37%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>74925</t>
+          <t>75438</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>100281</t>
+          <t>99698</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,22%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>60152</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>50273</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>68557</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>42,86%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>35,82%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>48,85%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>55187</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>45962</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>64719</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>46011</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>64174</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>43,27%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>36,03%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>50,74%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60152</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>50583</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>69554</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>42,86%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>101386</t>
+          <t>103033</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>128471</t>
+          <t>128625</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>48,02%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>31477</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24450</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>40643</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>22,43%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>17,42%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>28,96%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>16887</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>11068</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>23987</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>11695</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>24090</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>13,24%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8,68%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>18,81%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>31477</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>24478</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>39894</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>22,43%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>38767</t>
+          <t>38543</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>59801</t>
+          <t>58739</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>21,93%</t>
         </is>
       </c>
     </row>
@@ -1061,72 +1061,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6191</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2763</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11390</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,41%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,12%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>3130</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1072</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6907</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1128</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6680</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,45%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,41%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>6191</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2950</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>11624</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,41%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5281</t>
+          <t>5203</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14875</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -1174,72 +1174,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5514</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2777</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>11063</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3,93%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>7,88%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>1355</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4847</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4267</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>1,06%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,8%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>5514</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2610</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>10617</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>3,93%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3288</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12266</t>
+          <t>12283</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>140333</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>140333</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>140333</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>140333</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>140333</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>140333</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>37864</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>30282</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>47898</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>18,63%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>14,9%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>23,56%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>46196</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>37252</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>56883</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>37380</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>56128</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>23,98%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>19,34%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>29,53%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>37864</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>30068</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>48587</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>18,63%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71548</t>
+          <t>72089</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>98551</t>
+          <t>97225</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,56%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>92455</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>81798</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>104247</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>45,48%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>40,24%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>51,28%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>143</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>96382</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>85803</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>108534</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>84150</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>106653</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>50,04%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>44,55%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>56,35%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>92455</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>80252</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>104092</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>45,48%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>174523</t>
+          <t>171464</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>205388</t>
+          <t>204100</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>51,55%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>51750</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>41831</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>61661</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>25,46%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>20,58%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>30,33%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>32846</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>24375</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>41060</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>24260</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>41799</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>17,05%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>12,65%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>21,32%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>51750</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>41365</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>61563</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>25,46%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>72427</t>
+          <t>71771</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>98450</t>
+          <t>96365</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,34%</t>
         </is>
       </c>
     </row>
@@ -1743,72 +1743,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15424</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10087</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>21729</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7,59%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,96%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,69%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>6308</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2885</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>11416</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3312</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>11717</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,27%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,93%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>15424</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>9932</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>21858</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>7,59%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14780</t>
+          <t>15688</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29492</t>
+          <t>30074</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -1856,72 +1856,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5778</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2835</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>10626</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2,84%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>5,23%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>10889</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>5837</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>16121</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>6474</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>17870</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>5,65%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>8,37%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>5778</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>2612</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>10465</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11191</t>
+          <t>11298</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24343</t>
+          <t>24935</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>203271</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>203271</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>203271</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>284</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>192621</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>192621</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>192621</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>203271</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>203271</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>203271</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>74863</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>63319</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>87338</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>21,79%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>18,43%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>25,42%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>97185</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>83809</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>110781</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>84584</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>110734</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>30,35%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>26,18%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>34,6%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>74863</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>63770</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>87201</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>21,79%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>155151</t>
+          <t>154736</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>190342</t>
+          <t>190738</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,74%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>152606</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>138187</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>167855</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>44,41%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>40,22%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>48,85%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>151568</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>137355</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>166385</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>137232</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>165539</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>47,34%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>42,9%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>51,97%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>152606</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>137586</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>167172</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>282951</t>
+          <t>285005</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>326760</t>
+          <t>325338</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>49,01%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>83228</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>69691</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>95758</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>24,22%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>20,28%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>27,87%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>49733</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>39814</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>60500</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>39488</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>60629</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>15,53%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>12,44%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>18,9%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>83228</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>71119</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>97400</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>24,22%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>117505</t>
+          <t>117001</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>150349</t>
+          <t>149482</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,52%</t>
         </is>
       </c>
     </row>
@@ -2425,72 +2425,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>21615</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>15192</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>29959</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>6,29%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>4,42%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>8,72%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>9438</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>5399</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>15516</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>5478</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>15245</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>2,95%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>4,85%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>21615</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>15054</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>29753</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>6,29%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23044</t>
+          <t>23053</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>40010</t>
+          <t>40597</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -2538,72 +2538,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>11292</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>6516</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>17727</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>3,29%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>5,16%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>12244</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>7235</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>18948</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>7546</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>19421</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>3,82%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>5,92%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>11292</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>6760</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>17359</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>3,29%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17375</t>
+          <t>17168</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>32517</t>
+          <t>32853</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>516</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>343604</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>343604</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>343604</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>475</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>320168</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>320168</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>320168</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>516</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>343604</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>343604</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>343604</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2813,13 +2813,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de que le haya gustado ir al colegio, percibida por el adulto en 2012 (tasa de respuesta: 98,02%)</t>
+          <t>Menores según la frecuencia de que le haya gustado ir al colegio, percibida por el/la adulto/a [KIDSCREEN 20] en 2012 (tasa de respuesta: 98,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2830,7 +2830,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2998,72 +2998,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>65900</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>55537</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>76491</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>42,06%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>35,45%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>48,82%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>77640</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>67154</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>88281</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>66957</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>87991</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>49,92%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>43,18%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>56,77%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>65900</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>57183</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>77968</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>42,06%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>129806</t>
+          <t>128951</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>158882</t>
+          <t>157223</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,36%</t>
         </is>
       </c>
     </row>
@@ -3111,72 +3111,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>59550</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>49562</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>69930</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>38,01%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>31,63%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>44,63%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>58321</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>47868</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>68071</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>48450</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>68365</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>37,5%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>30,78%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>43,77%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>59550</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>49652</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>69157</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>38,01%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>104124</t>
+          <t>104645</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>132249</t>
+          <t>133032</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,61%</t>
         </is>
       </c>
     </row>
@@ -3224,72 +3224,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17957</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12039</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>25329</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>11,46%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>7,68%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>16,17%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>13213</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>8113</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>20594</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>8220</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>20058</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>8,5%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,22%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>13,24%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>17957</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>12156</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>25195</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>11,46%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>22401</t>
+          <t>23346</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>40250</t>
+          <t>40559</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -3337,72 +3337,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9356</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5118</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>14677</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,97%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,37%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>4090</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1514</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8749</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1451</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>8829</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,63%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,63%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>9356</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>5303</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>15535</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,97%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8565</t>
+          <t>8414</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19477</t>
+          <t>20265</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -3450,72 +3450,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3911</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1318</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8552</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>5,46%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>2250</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>651</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6297</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>6494</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>1,45%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,42%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4,05%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>3911</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1326</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>8024</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2643</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11050</t>
+          <t>11584</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -3563,57 +3563,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156674</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156674</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156674</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>155514</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>155514</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>155514</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>156674</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>156674</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>156674</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3680,72 +3680,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>52965</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>44124</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>64868</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>30,12%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>25,09%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>36,89%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>56889</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>48014</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>67072</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>47246</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>66783</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>34,31%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>28,96%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>40,45%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>52965</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>43336</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>62968</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>30,12%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>97304</t>
+          <t>96187</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>124927</t>
+          <t>123390</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,12%</t>
         </is>
       </c>
     </row>
@@ -3793,72 +3793,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>71313</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>61124</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>82537</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>40,56%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>34,76%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>46,94%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>68161</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>57268</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>78550</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>57971</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>78451</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>41,11%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>34,54%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>47,38%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>71313</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>61714</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>83046</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>40,56%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>124548</t>
+          <t>123413</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>154294</t>
+          <t>154900</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,34%</t>
         </is>
       </c>
     </row>
@@ -3906,72 +3906,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>31811</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>22896</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>41178</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>18,09%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>13,02%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>23,42%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>29328</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>21522</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>37808</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>22047</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>38245</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>17,69%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>12,98%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>22,8%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>31811</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>24439</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>40469</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>18,09%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>50640</t>
+          <t>49546</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>73961</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,94%</t>
         </is>
       </c>
     </row>
@@ -4019,72 +4019,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12775</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7753</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>19166</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7,27%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,41%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,9%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>7007</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3469</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>12528</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3521</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>12517</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>4,23%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,56%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>12775</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>7350</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>19112</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>7,27%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13672</t>
+          <t>13931</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27000</t>
+          <t>28926</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -4132,72 +4132,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6970</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3678</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>11959</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3,96%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6,8%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>4411</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1937</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8891</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1867</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>8418</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>2,66%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>5,36%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>6970</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>3551</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>12266</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>3,96%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7175</t>
+          <t>7047</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18048</t>
+          <t>17361</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -4245,57 +4245,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>175834</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>175834</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>175834</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>165796</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>165796</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>165796</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>175834</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>175834</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>175834</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4362,72 +4362,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>118864</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>104091</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>132670</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>35,75%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>31,3%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>39,9%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>134529</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>120696</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>149292</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>120009</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>149732</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>41,87%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>37,56%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>46,46%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>118864</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>104501</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>132896</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>35,75%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>233502</t>
+          <t>233491</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>273217</t>
+          <t>274666</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>42,01%</t>
         </is>
       </c>
     </row>
@@ -4475,107 +4475,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>130863</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>116985</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>144890</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>39,36%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>35,18%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>43,58%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>126482</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>111892</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>141332</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>111666</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>141154</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>39,36%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>34,82%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>43,99%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>130863</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>117260</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>147285</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>34,75%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>43,93%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>257345</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>237252</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>277819</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
         <is>
           <t>39,36%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>35,27%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>44,3%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>257345</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>238457</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>279346</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>39,36%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,49%</t>
         </is>
       </c>
     </row>
@@ -4588,107 +4588,107 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>49768</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39550</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>60019</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>14,97%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>11,89%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>18,05%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>42542</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>32896</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>54118</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>33128</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>53169</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>13,24%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>10,24%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>16,84%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>49768</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>40144</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>61728</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>14,97%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
+          <t>10,31%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>16,55%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>92310</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>78905</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>107778</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>14,12%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
           <t>12,07%</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>18,56%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>92310</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>78422</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>106689</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>14,12%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>11,99%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -4701,107 +4701,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>22131</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>15722</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>30090</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>6,66%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>4,73%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>9,05%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>11097</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>6803</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>17961</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>6136</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>16948</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>3,45%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>5,59%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>22131</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>15284</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>30280</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>1,91%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>5,27%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>33228</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>24671</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>43520</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>5,08%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
         <is>
           <t>6,66%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>4,6%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>9,11%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>33228</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>24675</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>43643</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>5,08%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>3,77%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -4814,72 +4814,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>10881</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>6844</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>17044</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>5,13%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>6660</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>3308</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>11985</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>3337</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>11761</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>2,07%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>10881</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>6221</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>16929</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>3,27%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11989</t>
+          <t>11674</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>24955</t>
+          <t>25036</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -4927,57 +4927,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>332508</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>332508</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>332508</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>456</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>321310</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>321310</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>321310</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>332508</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>332508</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>332508</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5089,13 +5089,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de que le haya gustado ir al colegio, percibida por el adulto en 2016 (tasa de respuesta: 98,62%)</t>
+          <t>Menores según la frecuencia de que le haya gustado ir al colegio, percibida por el/la adulto/a [KIDSCREEN 20] en 2016 (tasa de respuesta: 98,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5106,7 +5106,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5274,72 +5274,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>81888</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>70952</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>93027</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>44,18%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>38,28%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>50,19%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>85655</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>74362</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>96653</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>74914</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>98022</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>46,25%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>40,16%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>52,19%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>81888</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>71847</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>93602</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>44,18%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>151608</t>
+          <t>151293</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>182652</t>
+          <t>183826</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,61%</t>
         </is>
       </c>
     </row>
@@ -5387,72 +5387,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>62851</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>52694</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>75181</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>33,91%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>28,43%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>40,56%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>66270</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>56776</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>77927</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>56216</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>76955</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>35,79%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>30,66%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>42,08%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>62851</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>52364</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>73808</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>33,91%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>113876</t>
+          <t>114388</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>145496</t>
+          <t>145369</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,23%</t>
         </is>
       </c>
     </row>
@@ -5500,72 +5500,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>27707</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20583</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>36191</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>14,95%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>11,11%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>19,53%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>23975</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>17087</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>32060</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>17161</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>32078</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>12,95%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,23%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>17,31%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>27707</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>20533</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>36446</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>14,95%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>41490</t>
+          <t>41662</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>63707</t>
+          <t>62909</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,98%</t>
         </is>
       </c>
     </row>
@@ -5613,72 +5613,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7653</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3864</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13671</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,13%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,38%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>6635</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2879</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>11962</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2876</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>12299</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,58%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>1,55%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,46%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>7653</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>3985</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>13220</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,13%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9157</t>
+          <t>8949</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22030</t>
+          <t>21855</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -5726,107 +5726,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5243</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2173</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9956</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2,83%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>5,37%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>2647</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>659</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6513</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>658</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>7250</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>1,43%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>5243</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2103</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>9820</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>7890</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>4175</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>13678</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>1,13%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>7890</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>4164</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>13891</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -5839,57 +5839,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>185342</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>185342</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>185342</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>266</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>185183</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>185183</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>185183</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>185342</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>185342</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>185342</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5956,72 +5956,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>47403</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>37931</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>58179</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>27,24%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>21,79%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>33,43%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>63496</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>53039</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>73618</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>52392</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>74540</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>37,18%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>31,06%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>43,1%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>47403</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>37542</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>58684</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>27,24%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>97377</t>
+          <t>97335</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>126498</t>
+          <t>125685</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,45%</t>
         </is>
       </c>
     </row>
@@ -6069,72 +6069,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>75995</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>64679</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>86666</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>43,66%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>37,16%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>49,79%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>65672</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>54882</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>75848</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>56430</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>77444</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>38,45%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>32,13%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>75995</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>65503</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>86078</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>43,66%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>127015</t>
+          <t>125285</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>157217</t>
+          <t>157189</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>45,58%</t>
         </is>
       </c>
     </row>
@@ -6182,72 +6182,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>39121</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>30146</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>49285</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>22,48%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>17,32%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>28,32%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>31226</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>23791</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>40288</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>23321</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>40718</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>18,28%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>13,93%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>23,59%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>39121</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>30077</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>48710</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>22,48%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>59113</t>
+          <t>58854</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>83674</t>
+          <t>83255</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,14%</t>
         </is>
       </c>
     </row>
@@ -6295,72 +6295,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9491</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5022</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>15163</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,45%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,71%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>6611</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3370</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>11887</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3486</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>11816</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,87%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>9491</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>5224</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>15489</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,45%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10826</t>
+          <t>10272</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24100</t>
+          <t>24022</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -6408,72 +6408,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2039</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5475</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>3785</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1380</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8468</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1276</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>8306</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>2,22%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>4,96%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2039</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>629</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>5395</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>2757</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11260</t>
+          <t>11182</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -6521,57 +6521,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>170789</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>170789</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>170789</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6638,72 +6638,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>129291</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>114189</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>144944</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>35,98%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>31,77%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>40,33%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>214</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>149151</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>135310</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>165324</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>134182</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>165067</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>41,9%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>38,01%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>46,44%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>129291</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>114693</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>144308</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>35,98%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>256098</t>
+          <t>255678</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>299026</t>
+          <t>301766</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>42,18%</t>
         </is>
       </c>
     </row>
@@ -6751,72 +6751,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>138845</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>121843</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>153384</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>38,63%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>33,9%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>42,68%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>131942</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>118538</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>147470</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>115763</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>147189</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>37,07%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>33,3%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>41,43%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>138845</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>124475</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>154859</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>38,63%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>251404</t>
+          <t>248937</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>292480</t>
+          <t>291145</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>40,7%</t>
         </is>
       </c>
     </row>
@@ -6864,74 +6864,74 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>66828</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>55241</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>79057</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>18,59%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>15,37%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>22,0%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>55201</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>44990</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>67441</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>44329</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>66166</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>15,51%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>12,64%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>18,95%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>66828</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>55405</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>79626</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>12,45%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>18,59%</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>15,42%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>22,16%</t>
-        </is>
-      </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>173</t>
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>106447</t>
+          <t>105839</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>141391</t>
+          <t>139544</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,51%</t>
         </is>
       </c>
     </row>
@@ -6977,72 +6977,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>17144</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>11189</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>25414</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>4,77%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>3,11%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>7,07%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>13247</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>8088</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>20035</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>8278</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>19243</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>3,72%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>5,63%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>17144</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>11246</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>24424</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>4,77%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22158</t>
+          <t>22624</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>40372</t>
+          <t>40941</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -7090,72 +7090,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>7282</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3460</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>12863</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>3,58%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>6432</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>3119</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>11096</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>3337</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>12149</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>1,81%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>7282</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>3472</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>12709</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8187</t>
+          <t>8291</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20822</t>
+          <t>21578</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -7203,57 +7203,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>359389</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>359389</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>359389</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>355972</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>355972</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>355972</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>493</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>359389</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>359389</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>359389</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
